--- a/data/project_data.xlsx
+++ b/data/project_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckourouklis.EDYMET\Downloads\map-main_1\map-main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mouhq-my.sharepoint.com/personal/ckourouklis_mou_gr/Documents/Qgis/1. Page combo Telika/rail_map-main_1/map-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CFD466-D2BC-4F71-A635-5CA72F8FB78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{5FD5538B-BDA2-43B1-A68F-91BE75BA4E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBDC192E-E498-4D46-A4C9-12D8982AA211}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1206,7 +1206,7 @@
     <t>Ο converter τη διαβάζει αυτόματα και εμφανίζεται σαν ετικέτα πάνω δεξιά στον χάρτη.</t>
   </si>
   <si>
-    <t>06/08/2026</t>
+    <t>06/06/2026</t>
   </si>
 </sst>
 </file>
@@ -1624,13 +1624,14 @@
   <dimension ref="A1:O26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="18" style="12" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="55" customWidth="1"/>
-    <col min="7" max="8" width="18" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
     <col min="11" max="11" width="26" customWidth="1"/>
@@ -1656,7 +1657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1703,7 +1704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -2725,6 +2726,7 @@
   </sheetData>
   <autoFilter ref="A1:O24" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
